--- a/data/normalized/basidia.xlsx
+++ b/data/normalized/basidia.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hensley/Desktop/wiscam_microscopy/data/normalized/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D2E3866-E84C-6A46-9930-B9FB498162F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7473243D-FCF5-3C4D-898F-4A5A9846618E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-33880" yWindow="520" windowWidth="28040" windowHeight="17140" xr2:uid="{A37A3200-206F-D948-B180-E6EBD0F013C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -731,7 +731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -740,11 +740,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1145,48 +1144,6 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
-        <v>24</v>
-      </c>
-      <c r="E2">
-        <v>24</v>
-      </c>
-      <c r="F2">
-        <v>31</v>
-      </c>
-      <c r="G2">
-        <v>40</v>
-      </c>
-      <c r="H2">
-        <v>6.5</v>
-      </c>
-      <c r="I2">
-        <v>8.5</v>
-      </c>
-      <c r="J2">
-        <v>10</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>24</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>2</v>
-      </c>
-      <c r="P2">
-        <v>5.9</v>
-      </c>
-      <c r="Q2">
-        <v>8.5</v>
-      </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1197,48 +1154,6 @@
       </c>
       <c r="C3" t="s">
         <v>5</v>
-      </c>
-      <c r="D3">
-        <v>25</v>
-      </c>
-      <c r="E3">
-        <v>40</v>
-      </c>
-      <c r="F3">
-        <v>44.8</v>
-      </c>
-      <c r="G3">
-        <v>52</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>12.7</v>
-      </c>
-      <c r="J3">
-        <v>15.5</v>
-      </c>
-      <c r="K3">
-        <v>13</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>10</v>
-      </c>
-      <c r="N3" s="6">
-        <v>0</v>
-      </c>
-      <c r="O3" s="6">
-        <v>3</v>
-      </c>
-      <c r="P3" s="6">
-        <v>5.5</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>9.6</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">

--- a/data/normalized/basidia.xlsx
+++ b/data/normalized/basidia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hensley/Desktop/wiscam_microscopy/data/normalized/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7473243D-FCF5-3C4D-898F-4A5A9846618E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26706130-1632-FB44-AEE2-AC74354C398F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33880" yWindow="520" windowWidth="28040" windowHeight="17140" xr2:uid="{A37A3200-206F-D948-B180-E6EBD0F013C5}"/>
+    <workbookView xWindow="1360" yWindow="680" windowWidth="28040" windowHeight="17140" xr2:uid="{A37A3200-206F-D948-B180-E6EBD0F013C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1080,6 +1080,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{242BE431-9CF5-744A-83E8-A5EDEC306196}">
   <dimension ref="A1:Q145"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="48.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -1136,230 +1139,227 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>172</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>173</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
         <v>43</v>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
         <v>43</v>
@@ -1378,285 +1378,285 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>176</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>156</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>180</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>138</v>
       </c>
       <c r="B41" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="C49" t="s">
         <v>43</v>
@@ -1664,21 +1664,21 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="B51" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="C51" t="s">
         <v>43</v>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="B52" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="C52" t="s">
         <v>43</v>
@@ -1697,21 +1697,21 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B53" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="B54" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="B55" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="B56" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="C56" t="s">
         <v>43</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="C57" t="s">
         <v>43</v>
@@ -1752,21 +1752,21 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="C59" t="s">
         <v>43</v>
@@ -1774,29 +1774,29 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C60" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="B61" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="C61" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="B62" t="s">
         <v>23</v>
@@ -1807,54 +1807,54 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B64" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B65" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
@@ -1862,164 +1862,164 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B68" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C68" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C69" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C72" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="B73" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="B74" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="C74" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="B75" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="B76" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="B77" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="B78" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="B79" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="B80" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="B82" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -2027,54 +2027,54 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B83" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="C83" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C84" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="C85" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="B86" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="C86" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="B87" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
@@ -2082,43 +2082,43 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="C88" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="B89" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="C89" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="B90" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="C90" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="B91" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="C91" t="s">
         <v>43</v>
@@ -2126,65 +2126,65 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="B92" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C92" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B93" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C93" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B94" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C94" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="C95" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="B96" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C96" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="B97" t="s">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -2192,73 +2192,73 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="B98" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C98" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="B99" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C99" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="B100" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="C100" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="B101" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="C101" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="C102" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B103" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C103" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B104" t="s">
         <v>16</v>
@@ -2269,428 +2269,428 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B105" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C105" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B106" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C106" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="B107" t="s">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="C107" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="B108" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C108" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="B109" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C109" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="C110" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="B111" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="C111" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C112" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="B113" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C113" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="B114" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C114" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="B115" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C115" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="B116" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C116" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="B117" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="C117" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="B118" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C118" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="B119" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C119" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>164</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="B121" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="C121" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B122" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="C122" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="C123" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>168</v>
+        <v>38</v>
       </c>
       <c r="B124" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="C124" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>169</v>
+        <v>46</v>
       </c>
       <c r="B125" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C125" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>170</v>
+        <v>47</v>
       </c>
       <c r="B126" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C126" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="B127" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C127" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B128" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C128" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="B129" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C129" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="B130" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C130" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="B131" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C131" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="B132" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C132" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B133" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="C133" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>178</v>
+        <v>6</v>
       </c>
       <c r="B134" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>179</v>
+        <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="C135" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>180</v>
+        <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="B137" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>58</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="C138" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="C139" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="B140" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C140" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>185</v>
+        <v>93</v>
       </c>
       <c r="B141" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C141" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B142" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C142" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>187</v>
+        <v>30</v>
       </c>
       <c r="B143" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="C143" t="s">
         <v>14</v>
@@ -2698,18 +2698,24 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+      <c r="B144" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>188</v>
       </c>
-      <c r="B145" t="s">
-        <v>189</v>
-      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q145">
+    <sortCondition ref="B1:B145"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/normalized/basidia.xlsx
+++ b/data/normalized/basidia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hensley/Desktop/wiscam_microscopy/data/normalized/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26706130-1632-FB44-AEE2-AC74354C398F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5096B0B0-64AA-AA48-8217-F23030726A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="680" windowWidth="28040" windowHeight="17140" xr2:uid="{A37A3200-206F-D948-B180-E6EBD0F013C5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="202">
   <si>
     <t>specimen_id</t>
   </si>
@@ -600,12 +600,6 @@
   </si>
   <si>
     <t>30280_7</t>
-  </si>
-  <si>
-    <t>nan</t>
-  </si>
-  <si>
-    <t>31+ species</t>
   </si>
   <si>
     <t>min_length</t>
@@ -1078,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{242BE431-9CF5-744A-83E8-A5EDEC306196}">
-  <dimension ref="A1:Q145"/>
+  <dimension ref="A1:Q143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="48.83203125" customWidth="1"/>
@@ -1095,70 +1089,73 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="L1" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -1169,7 +1166,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
@@ -1180,7 +1177,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -1191,7 +1188,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
@@ -1202,7 +1199,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
         <v>52</v>
@@ -1213,7 +1210,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
         <v>52</v>
@@ -1224,7 +1221,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s">
         <v>52</v>
@@ -1235,7 +1232,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B11" t="s">
         <v>52</v>
@@ -1246,10 +1243,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
         <v>43</v>
@@ -1257,7 +1254,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
         <v>82</v>
@@ -1268,7 +1265,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
         <v>82</v>
@@ -1279,7 +1276,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
         <v>82</v>
@@ -1290,7 +1287,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s">
         <v>82</v>
@@ -1301,7 +1298,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="B17" t="s">
         <v>82</v>
@@ -1312,7 +1309,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B18" t="s">
         <v>82</v>
@@ -1323,7 +1320,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B19" t="s">
         <v>82</v>
@@ -1334,7 +1331,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B20" t="s">
         <v>82</v>
@@ -1345,7 +1342,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B21" t="s">
         <v>82</v>
@@ -1356,7 +1353,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B22" t="s">
         <v>82</v>
@@ -1367,7 +1364,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B23" t="s">
         <v>82</v>
@@ -1378,18 +1375,18 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
         <v>29</v>
@@ -1400,7 +1397,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="B26" t="s">
         <v>29</v>
@@ -1411,7 +1408,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s">
         <v>29</v>
@@ -1422,7 +1419,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s">
         <v>29</v>
@@ -1433,7 +1430,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s">
         <v>29</v>
@@ -1444,18 +1441,18 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
@@ -1466,7 +1463,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
@@ -1477,7 +1474,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B33" t="s">
         <v>33</v>
@@ -1488,7 +1485,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" t="s">
         <v>33</v>
@@ -1499,10 +1496,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -1510,7 +1507,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
@@ -1521,7 +1518,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
@@ -1532,7 +1529,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
@@ -1543,7 +1540,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
@@ -1554,7 +1551,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
@@ -1565,18 +1562,18 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="B41" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B42" t="s">
         <v>104</v>
@@ -1587,7 +1584,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B43" t="s">
         <v>104</v>
@@ -1598,7 +1595,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B44" t="s">
         <v>104</v>
@@ -1609,7 +1606,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B45" t="s">
         <v>104</v>
@@ -1620,7 +1617,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
         <v>104</v>
@@ -1631,7 +1628,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B47" t="s">
         <v>104</v>
@@ -1642,7 +1639,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B48" t="s">
         <v>104</v>
@@ -1653,7 +1650,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B49" t="s">
         <v>104</v>
@@ -1664,10 +1661,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="C50" t="s">
         <v>43</v>
@@ -1675,7 +1672,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B51" t="s">
         <v>150</v>
@@ -1686,18 +1683,18 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B53" t="s">
         <v>101</v>
@@ -1708,7 +1705,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="B54" t="s">
         <v>101</v>
@@ -1719,18 +1716,18 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>179</v>
+        <v>41</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B56" t="s">
         <v>42</v>
@@ -1741,7 +1738,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B57" t="s">
         <v>42</v>
@@ -1752,7 +1749,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="B58" t="s">
         <v>42</v>
@@ -1763,10 +1760,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B59" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="C59" t="s">
         <v>43</v>
@@ -1774,7 +1771,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="B60" t="s">
         <v>92</v>
@@ -1785,18 +1782,18 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B62" t="s">
         <v>23</v>
@@ -1807,7 +1804,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="B63" t="s">
         <v>23</v>
@@ -1818,7 +1815,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B64" t="s">
         <v>23</v>
@@ -1829,7 +1826,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="B65" t="s">
         <v>23</v>
@@ -1840,18 +1837,18 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B67" t="s">
         <v>99</v>
@@ -1862,7 +1859,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B68" t="s">
         <v>99</v>
@@ -1873,18 +1870,18 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B70" t="s">
         <v>71</v>
@@ -1895,7 +1892,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B71" t="s">
         <v>71</v>
@@ -1906,7 +1903,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="B72" t="s">
         <v>71</v>
@@ -1917,7 +1914,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B73" t="s">
         <v>71</v>
@@ -1928,7 +1925,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B74" t="s">
         <v>71</v>
@@ -1939,10 +1936,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -1950,7 +1947,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B76" t="s">
         <v>27</v>
@@ -1961,7 +1958,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B77" t="s">
         <v>27</v>
@@ -1972,7 +1969,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B78" t="s">
         <v>27</v>
@@ -1983,7 +1980,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B79" t="s">
         <v>27</v>
@@ -1994,29 +1991,29 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C80" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="C81" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="B82" t="s">
         <v>75</v>
@@ -2027,7 +2024,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="B83" t="s">
         <v>75</v>
@@ -2038,7 +2035,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="B84" t="s">
         <v>75</v>
@@ -2049,7 +2046,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B85" t="s">
         <v>75</v>
@@ -2060,7 +2057,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B86" t="s">
         <v>75</v>
@@ -2071,7 +2068,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B87" t="s">
         <v>75</v>
@@ -2082,7 +2079,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B88" t="s">
         <v>75</v>
@@ -2093,7 +2090,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B89" t="s">
         <v>75</v>
@@ -2104,18 +2101,18 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>187</v>
+        <v>44</v>
       </c>
       <c r="B90" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B91" t="s">
         <v>45</v>
@@ -2126,7 +2123,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="B92" t="s">
         <v>45</v>
@@ -2137,7 +2134,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B93" t="s">
         <v>45</v>
@@ -2148,18 +2145,18 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="B94" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C94" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B95" t="s">
         <v>21</v>
@@ -2170,7 +2167,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B96" t="s">
         <v>21</v>
@@ -2181,7 +2178,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="B97" t="s">
         <v>21</v>
@@ -2192,18 +2189,18 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="B98" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B99" t="s">
         <v>88</v>
@@ -2214,7 +2211,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="B100" t="s">
         <v>88</v>
@@ -2225,18 +2222,18 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="B101" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="C101" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>15</v>
+        <v>143</v>
       </c>
       <c r="B102" t="s">
         <v>16</v>
@@ -2247,7 +2244,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B103" t="s">
         <v>16</v>
@@ -2258,7 +2255,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B104" t="s">
         <v>16</v>
@@ -2269,10 +2266,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="C105" t="s">
         <v>14</v>
@@ -2280,10 +2277,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="B106" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
@@ -2291,18 +2288,18 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="B107" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C107" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B108" t="s">
         <v>77</v>
@@ -2313,7 +2310,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="B109" t="s">
         <v>77</v>
@@ -2324,7 +2321,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="B110" t="s">
         <v>77</v>
@@ -2335,7 +2332,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B111" t="s">
         <v>77</v>
@@ -2346,18 +2343,18 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="B112" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C112" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="B113" t="s">
         <v>57</v>
@@ -2368,43 +2365,43 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B114" t="s">
         <v>57</v>
       </c>
       <c r="C114" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="B115" t="s">
         <v>57</v>
       </c>
       <c r="C115" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="B116" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="C116" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="B117" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="C117" t="s">
         <v>14</v>
@@ -2412,7 +2409,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B118" t="s">
         <v>62</v>
@@ -2423,10 +2420,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C119" t="s">
         <v>14</v>
@@ -2434,10 +2431,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="C120" t="s">
         <v>14</v>
@@ -2445,40 +2442,40 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B121" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C121" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C122" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>38</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="C123" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B124" t="s">
         <v>39</v>
@@ -2489,7 +2486,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B125" t="s">
         <v>39</v>
@@ -2500,7 +2497,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="B126" t="s">
         <v>39</v>
@@ -2511,7 +2508,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="B127" t="s">
         <v>39</v>
@@ -2522,7 +2519,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B128" t="s">
         <v>39</v>
@@ -2533,7 +2530,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B129" t="s">
         <v>39</v>
@@ -2544,7 +2541,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B130" t="s">
         <v>39</v>
@@ -2555,7 +2552,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B131" t="s">
         <v>39</v>
@@ -2566,7 +2563,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B132" t="s">
         <v>39</v>
@@ -2577,10 +2574,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="B133" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="C133" t="s">
         <v>5</v>
@@ -2588,7 +2585,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
@@ -2599,7 +2596,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B135" t="s">
         <v>7</v>
@@ -2610,7 +2607,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="B136" t="s">
         <v>7</v>
@@ -2621,7 +2618,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B137" t="s">
         <v>7</v>
@@ -2632,7 +2629,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B138" t="s">
         <v>7</v>
@@ -2643,29 +2640,29 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="B139" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C139" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B140" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C140" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="B141" t="s">
         <v>94</v>
@@ -2676,18 +2673,18 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>177</v>
+        <v>30</v>
       </c>
       <c r="B142" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="C142" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>30</v>
+        <v>158</v>
       </c>
       <c r="B143" t="s">
         <v>31</v>
@@ -2696,25 +2693,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>158</v>
-      </c>
-      <c r="B144" t="s">
-        <v>31</v>
-      </c>
-      <c r="C144" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>188</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q145">
-    <sortCondition ref="B1:B145"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q144">
+    <sortCondition ref="B1:B144"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
